--- a/tests/data/xlsx/xlsx_comments.xlsx
+++ b/tests/data/xlsx/xlsx_comments.xlsx
@@ -1,34 +1,153 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ceb/git/docling-3/tests/data/xlsx/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ED46F2A-5D23-D74E-B2A0-4FAF268BC642}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="10860" yWindow="2920" windowWidth="34560" windowHeight="22340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>John Reviewer</author>
+    <author>Jane Editor</author>
+    <author>tc={04C1C54B-2744-A647-93D1-A99C27C7EFDC}</author>
+    <author>tc={3A26E9AE-8B38-864D-BAF4-BA5D9C6E1DA4}</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Why Python specifically?</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B2" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>Which libraries are you referring to?</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F7" authorId="2" shapeId="0" xr:uid="{04C1C54B-2744-A647-93D1-A99C27C7EFDC}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Minimum number of saltwater ducks
+Reply:
+    I never thought it would be so low</t>
+      </text>
+    </comment>
+    <comment ref="G12" authorId="3" shapeId="0" xr:uid="{3A26E9AE-8B38-864D-BAF4-BA5D9C6E1DA4}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Maximum number of ducks</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+  <si>
+    <t>Python is great</t>
+  </si>
+  <si>
+    <t>Machine learning libraries</t>
+  </si>
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>Freshwater Ducks</t>
+  </si>
+  <si>
+    <t>Saltwater Ducks</t>
+  </si>
+  <si>
+    <t>Ducks</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
+      <color rgb="FF333333"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF333333"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,103 +165,32 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>John Reviewer</author>
-    <author>Jane Editor</author>
-  </authors>
-  <commentList>
-    <comment ref="A1" authorId="0" shapeId="0">
-      <text>
-        <t>Why Python specifically?</t>
-      </text>
-    </comment>
-    <comment ref="B2" authorId="1" shapeId="0">
-      <text>
-        <t>Which libraries are you referring to?</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Jane Smith (JS)" id="{ED88F4F5-A552-4A41-970D-6B23DC2319F4}" userId="Jane Smith (JS)" providerId="None"/>
+  <person displayName="Marcus Sterling (MS)" id="{F91C2EA4-71EE-4B4A-B219-115641A7AB48}" userId="Marcus Sterling (MS)" providerId="None"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -428,31 +476,135 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="F7" dT="2026-06-18T17:12:37.41" personId="{ED88F4F5-A552-4A41-970D-6B23DC2319F4}" id="{04C1C54B-2744-A647-93D1-A99C27C7EFDC}">
+    <text>Minimum number of saltwater ducks</text>
+  </threadedComment>
+  <threadedComment ref="F7" dT="2026-06-18T17:15:52.31" personId="{F91C2EA4-71EE-4B4A-B219-115641A7AB48}" id="{9079903E-5C85-DC40-828F-9D93A620480C}" parentId="{04C1C54B-2744-A647-93D1-A99C27C7EFDC}">
+    <text>I never thought it would be so low</text>
+  </threadedComment>
+  <threadedComment ref="G12" dT="2026-06-18T17:12:57.35" personId="{ED88F4F5-A552-4A41-970D-6B23DC2319F4}" id="{3A26E9AE-8B38-864D-BAF4-BA5D9C6E1DA4}">
+    <text>Maximum number of ducks</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G12"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Python is great</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Machine learning libraries</t>
-        </is>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="D6" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="D7" s="1">
+        <v>2019</v>
+      </c>
+      <c r="E7" s="1">
+        <v>120</v>
+      </c>
+      <c r="F7" s="1">
+        <v>80</v>
+      </c>
+      <c r="G7" s="1">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="D8" s="1">
+        <v>2020</v>
+      </c>
+      <c r="E8" s="1">
+        <v>135</v>
+      </c>
+      <c r="F8" s="1">
+        <v>95</v>
+      </c>
+      <c r="G8" s="1">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="D9" s="1">
+        <v>2021</v>
+      </c>
+      <c r="E9" s="1">
+        <v>150</v>
+      </c>
+      <c r="F9" s="1">
+        <v>100</v>
+      </c>
+      <c r="G9" s="1">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="D10" s="1">
+        <v>2022</v>
+      </c>
+      <c r="E10" s="1">
+        <v>170</v>
+      </c>
+      <c r="F10" s="1">
+        <v>110</v>
+      </c>
+      <c r="G10" s="1">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="D11" s="1">
+        <v>2023</v>
+      </c>
+      <c r="E11" s="1">
+        <v>160</v>
+      </c>
+      <c r="F11" s="1">
+        <v>120</v>
+      </c>
+      <c r="G11" s="1">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="D12" s="1">
+        <v>2024</v>
+      </c>
+      <c r="E12" s="1">
+        <v>180</v>
+      </c>
+      <c r="F12" s="1">
+        <v>130</v>
+      </c>
+      <c r="G12" s="1">
+        <v>310</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>